--- a/data/Book1.xlsx
+++ b/data/Book1.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sonir\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sonir\Downloads\snake_game_v2\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB92C79D-5401-472B-AAB5-A5AE7F56528C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2424D7-F8EA-4AFA-8615-0E56B99FACF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{70D0A116-D27A-458B-9A0C-5A6A446D71F4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{70D0A116-D27A-458B-9A0C-5A6A446D71F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1(25 May-31 May)" sheetId="4" r:id="rId1"/>
     <sheet name="Week 2(01 Jun - 07 Jun)" sheetId="3" r:id="rId2"/>
     <sheet name="Week 3(08 Jun - 15 Jun)" sheetId="2" r:id="rId3"/>
     <sheet name="Week 4(16 Jun - 22 Jun)" sheetId="1" r:id="rId4"/>
-    <sheet name="Mail info" sheetId="5" r:id="rId5"/>
+    <sheet name="Week 5(21 Jun-28 Jun)" sheetId="7" r:id="rId5"/>
+    <sheet name="Mail info" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="336">
   <si>
     <t>Ship Name</t>
   </si>
@@ -893,6 +894,187 @@
   </si>
   <si>
     <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>Avg. Speed</t>
+  </si>
+  <si>
+    <t>26-Jun-26</t>
+  </si>
+  <si>
+    <t>27-Jun-26</t>
+  </si>
+  <si>
+    <t>21-Jun-26</t>
+  </si>
+  <si>
+    <t>22-Jun-26</t>
+  </si>
+  <si>
+    <t>23-Jun-26</t>
+  </si>
+  <si>
+    <t>24-Jun-26</t>
+  </si>
+  <si>
+    <t>25-Jun-26</t>
+  </si>
+  <si>
+    <t>20-Jun-26</t>
+  </si>
+  <si>
+    <t>23:42</t>
+  </si>
+  <si>
+    <t>003B</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 204.11 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 231.93 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 213.12 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 215.64 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 202.10 g/kwh)</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>625N</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 217.98 g/kwh)</t>
+  </si>
+  <si>
+    <t>Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 3.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JNH-FES2604E </t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 35.25 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-21 23:15:00, Curr Start: 2026-06-20 12:00:00) | Report Info: 20-Jun-26 12:00</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 18.00 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-21 12:00:00, Curr Start: 2026-06-22 06:00:00) | Report Info: 22-Jun-26 06:00</t>
+  </si>
+  <si>
+    <t>04:18</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 13.88 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-22 14:25:00, Curr Start: 2026-06-23 04:18:00) | Report Info: 23-Jun-26 04:18</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 203.22 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 207.61 g/kwh)</t>
+  </si>
+  <si>
+    <t>Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.; Rule 7 (Reporting Gap): There is a 14.00 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-20 22:00:00, Curr Start: 2026-06-21 12:00:00) | Report Info: 21-Jun-26 12:00</t>
+  </si>
+  <si>
+    <t>31LA</t>
+  </si>
+  <si>
+    <t>18:48</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 25.00 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-26 19:48:00, Curr Start: 2026-06-25 18:48:00) | Report Info: 25-Jun-26 18:48</t>
+  </si>
+  <si>
+    <t>19:48</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 7.80 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-26 12:00:00, Curr Start: 2026-06-26 19:48:00) | Report Info: 26-Jun-26 19:48</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 2; Exhaust temp deviation &gt; ±50 from avg at Unit 4</t>
+  </si>
+  <si>
+    <t>004B26</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 2; Exhaust temp deviation &gt; ±50 from avg at Unit 3; Exhaust temp deviation &gt; ±50 from avg at Unit 8; SFOC out of 170-240 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 107.73 g/kwh); Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>004B</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 3; Exhaust temp deviation &gt; ±50 from avg at Unit 8; SFOC out of 170-240 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 107.73 g/kwh); Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 2; Exhaust temp deviation &gt; ±50 from avg at Unit 3; Exhaust temp deviation &gt; ±50 from avg at Unit 8; SFOC out of 170-240 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 111.29 g/kwh); Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 2; Exhaust temp deviation &gt; ±50 from avg at Unit 3; Exhaust temp deviation &gt; ±50 from avg at Unit 8; SFOC out of 170-240 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 97.80 g/kwh); Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.09) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 2; Exhaust temp deviation &gt; ±50 from avg at Unit 3; Exhaust temp deviation &gt; ±50 from avg at Unit 8; SFOC out of 170-240 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 94.51 g/kwh); Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>UARGFS2611</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 208.65 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 221.50 g/kwh)</t>
+  </si>
+  <si>
+    <t>uargfs2611</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 213.41 g/kwh)</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 48.00 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-25 00:00:00, Curr Start: 2026-06-23 00:00:00) | Report Info: 23-Jun-26 00:00</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 24.00 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-24 00:00:00, Curr Start: 2026-06-25 00:00:00) | Report Info: 25-Jun-26 00:00</t>
+  </si>
+  <si>
+    <t>02:12</t>
+  </si>
+  <si>
+    <t>03:48</t>
+  </si>
+  <si>
+    <t>UBCGFS2609</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 14.20 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-23 12:00:00, Curr Start: 2026-06-24 02:12:00) | Report Info: 24-Jun-26 02:12</t>
+  </si>
+  <si>
+    <t>09:36</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
 </sst>
 </file>
@@ -15162,11 +15344,3837 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E8A4A4-FA7E-46CA-80E4-4F6F8EC63AD9}">
+  <dimension ref="A1:AN42"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>278</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2">
+        <v>9614103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2">
+        <v>153</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>153</v>
+      </c>
+      <c r="M2">
+        <v>3780</v>
+      </c>
+      <c r="N2">
+        <v>97.7</v>
+      </c>
+      <c r="O2">
+        <v>39.9</v>
+      </c>
+      <c r="P2">
+        <v>12.3</v>
+      </c>
+      <c r="Q2">
+        <v>12.3</v>
+      </c>
+      <c r="R2">
+        <v>9.49</v>
+      </c>
+      <c r="S2">
+        <v>353</v>
+      </c>
+      <c r="T2">
+        <v>354</v>
+      </c>
+      <c r="U2">
+        <v>354</v>
+      </c>
+      <c r="V2">
+        <v>356</v>
+      </c>
+      <c r="W2">
+        <v>355</v>
+      </c>
+      <c r="X2">
+        <v>356</v>
+      </c>
+      <c r="AI2">
+        <v>51</v>
+      </c>
+      <c r="AJ2">
+        <v>204.1123585839033</v>
+      </c>
+      <c r="AK2">
+        <v>12.3</v>
+      </c>
+      <c r="AL2">
+        <v>12.44</v>
+      </c>
+      <c r="AM2">
+        <v>0.98722415795586527</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3">
+        <v>9504607</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3">
+        <v>314</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>314</v>
+      </c>
+      <c r="M3">
+        <v>4654.96</v>
+      </c>
+      <c r="N3">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="O3">
+        <v>21.49</v>
+      </c>
+      <c r="P3">
+        <v>24</v>
+      </c>
+      <c r="Q3">
+        <v>24</v>
+      </c>
+      <c r="R3">
+        <v>25.9</v>
+      </c>
+      <c r="S3">
+        <v>328</v>
+      </c>
+      <c r="T3">
+        <v>294</v>
+      </c>
+      <c r="U3">
+        <v>309</v>
+      </c>
+      <c r="V3">
+        <v>284</v>
+      </c>
+      <c r="W3">
+        <v>288</v>
+      </c>
+      <c r="X3">
+        <v>304</v>
+      </c>
+      <c r="AI3">
+        <v>112</v>
+      </c>
+      <c r="AJ3">
+        <v>231.83156604281601</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>13.08</v>
+      </c>
+      <c r="AM3">
+        <v>0.90226339216663509</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4">
+        <v>9504607</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" t="s">
+        <v>282</v>
+      </c>
+      <c r="G4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4">
+        <v>342</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>342</v>
+      </c>
+      <c r="M4">
+        <v>4658.3999999999996</v>
+      </c>
+      <c r="N4">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="O4">
+        <v>21.51</v>
+      </c>
+      <c r="P4">
+        <v>25</v>
+      </c>
+      <c r="Q4">
+        <v>23</v>
+      </c>
+      <c r="R4">
+        <v>27.01</v>
+      </c>
+      <c r="S4">
+        <v>329</v>
+      </c>
+      <c r="T4">
+        <v>296</v>
+      </c>
+      <c r="U4">
+        <v>313</v>
+      </c>
+      <c r="V4">
+        <v>291</v>
+      </c>
+      <c r="W4">
+        <v>301</v>
+      </c>
+      <c r="X4">
+        <v>305</v>
+      </c>
+      <c r="AI4">
+        <v>122</v>
+      </c>
+      <c r="AJ4">
+        <v>231.9251245062683</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>13.68</v>
+      </c>
+      <c r="AM4">
+        <v>0.94281298299845451</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5">
+        <v>9504607</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>282</v>
+      </c>
+      <c r="E5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" t="s">
+        <v>283</v>
+      </c>
+      <c r="G5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5">
+        <v>303</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>303</v>
+      </c>
+      <c r="M5">
+        <v>4852.6899999999996</v>
+      </c>
+      <c r="N5">
+        <v>64.2</v>
+      </c>
+      <c r="O5">
+        <v>22.4</v>
+      </c>
+      <c r="P5">
+        <v>23.4</v>
+      </c>
+      <c r="Q5">
+        <v>24</v>
+      </c>
+      <c r="R5">
+        <v>24.2</v>
+      </c>
+      <c r="S5">
+        <v>314</v>
+      </c>
+      <c r="T5">
+        <v>296</v>
+      </c>
+      <c r="U5">
+        <v>285</v>
+      </c>
+      <c r="V5">
+        <v>281</v>
+      </c>
+      <c r="W5">
+        <v>286</v>
+      </c>
+      <c r="X5">
+        <v>297</v>
+      </c>
+      <c r="AI5">
+        <v>115</v>
+      </c>
+      <c r="AJ5">
+        <v>213.11644349588249</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>12.63</v>
+      </c>
+      <c r="AM5">
+        <v>0.91146908685222505</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6">
+        <v>9504607</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6">
+        <v>36</v>
+      </c>
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6">
+        <v>215</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>215</v>
+      </c>
+      <c r="M6">
+        <v>4753.3900000000003</v>
+      </c>
+      <c r="N6">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="O6">
+        <v>21.95</v>
+      </c>
+      <c r="P6">
+        <v>18</v>
+      </c>
+      <c r="Q6">
+        <v>18</v>
+      </c>
+      <c r="R6">
+        <v>18.45</v>
+      </c>
+      <c r="S6">
+        <v>320</v>
+      </c>
+      <c r="T6">
+        <v>293</v>
+      </c>
+      <c r="U6">
+        <v>302</v>
+      </c>
+      <c r="V6">
+        <v>295</v>
+      </c>
+      <c r="W6">
+        <v>293</v>
+      </c>
+      <c r="X6">
+        <v>283</v>
+      </c>
+      <c r="AI6">
+        <v>84</v>
+      </c>
+      <c r="AJ6">
+        <v>215.63557797698061</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>11.94</v>
+      </c>
+      <c r="AM6">
+        <v>0.8835799292715304</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7">
+        <v>9504607</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>285</v>
+      </c>
+      <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" t="s">
+        <v>279</v>
+      </c>
+      <c r="G7" t="s">
+        <v>226</v>
+      </c>
+      <c r="H7">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7">
+        <v>280</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>280</v>
+      </c>
+      <c r="M7">
+        <v>5200</v>
+      </c>
+      <c r="N7">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="O7">
+        <v>24.01</v>
+      </c>
+      <c r="P7">
+        <v>22</v>
+      </c>
+      <c r="Q7">
+        <v>22</v>
+      </c>
+      <c r="R7">
+        <v>23.12</v>
+      </c>
+      <c r="S7">
+        <v>324</v>
+      </c>
+      <c r="T7">
+        <v>301</v>
+      </c>
+      <c r="U7">
+        <v>303</v>
+      </c>
+      <c r="V7">
+        <v>294</v>
+      </c>
+      <c r="W7">
+        <v>293</v>
+      </c>
+      <c r="X7">
+        <v>288</v>
+      </c>
+      <c r="AI7">
+        <v>102</v>
+      </c>
+      <c r="AJ7">
+        <v>202.09790209790211</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>12.73</v>
+      </c>
+      <c r="AM7">
+        <v>0.80244755244755239</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8">
+        <v>9464314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H8" t="s">
+        <v>295</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8">
+        <v>286</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>277</v>
+      </c>
+      <c r="M8">
+        <v>8315</v>
+      </c>
+      <c r="N8">
+        <v>60</v>
+      </c>
+      <c r="O8">
+        <v>23</v>
+      </c>
+      <c r="P8">
+        <v>24</v>
+      </c>
+      <c r="Q8">
+        <v>24</v>
+      </c>
+      <c r="R8">
+        <v>43.5</v>
+      </c>
+      <c r="S8">
+        <v>289</v>
+      </c>
+      <c r="T8">
+        <v>320</v>
+      </c>
+      <c r="U8">
+        <v>310</v>
+      </c>
+      <c r="V8">
+        <v>299</v>
+      </c>
+      <c r="W8">
+        <v>330</v>
+      </c>
+      <c r="X8">
+        <v>310</v>
+      </c>
+      <c r="Y8">
+        <v>320</v>
+      </c>
+      <c r="Z8">
+        <v>305</v>
+      </c>
+      <c r="AI8">
+        <v>245</v>
+      </c>
+      <c r="AJ8">
+        <v>217.97955502104631</v>
+      </c>
+      <c r="AK8">
+        <v>24</v>
+      </c>
+      <c r="AL8">
+        <v>11.92</v>
+      </c>
+      <c r="AM8">
+        <v>1.1049308478653039</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9">
+        <v>9395343</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>286</v>
+      </c>
+      <c r="E9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" t="s">
+        <v>281</v>
+      </c>
+      <c r="G9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9" t="s">
+        <v>298</v>
+      </c>
+      <c r="I9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>24</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10">
+        <v>9395343</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>282</v>
+      </c>
+      <c r="E10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F10" t="s">
+        <v>282</v>
+      </c>
+      <c r="G10" t="s">
+        <v>300</v>
+      </c>
+      <c r="H10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10">
+        <v>7</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="M10">
+        <v>4600</v>
+      </c>
+      <c r="N10">
+        <v>500</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10">
+        <v>8.42</v>
+      </c>
+      <c r="R10">
+        <v>2.1</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>152.17391304347831</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>7</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11">
+        <v>9395343</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" t="s">
+        <v>302</v>
+      </c>
+      <c r="F11" t="s">
+        <v>283</v>
+      </c>
+      <c r="G11" t="s">
+        <v>303</v>
+      </c>
+      <c r="H11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>8</v>
+      </c>
+      <c r="M11">
+        <v>2800</v>
+      </c>
+      <c r="N11">
+        <v>500</v>
+      </c>
+      <c r="O11">
+        <v>38</v>
+      </c>
+      <c r="P11">
+        <v>3.5</v>
+      </c>
+      <c r="Q11">
+        <v>3.37</v>
+      </c>
+      <c r="R11">
+        <v>2.5</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>255.10204081632651</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>6</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12">
+        <v>9485904</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>282</v>
+      </c>
+      <c r="E12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" t="s">
+        <v>283</v>
+      </c>
+      <c r="G12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12">
+        <v>331</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>289</v>
+      </c>
+      <c r="M12">
+        <v>3137</v>
+      </c>
+      <c r="N12">
+        <v>98</v>
+      </c>
+      <c r="O12">
+        <v>50</v>
+      </c>
+      <c r="P12">
+        <v>24</v>
+      </c>
+      <c r="Q12">
+        <v>24</v>
+      </c>
+      <c r="R12">
+        <v>15.3</v>
+      </c>
+      <c r="S12">
+        <v>361</v>
+      </c>
+      <c r="T12">
+        <v>352</v>
+      </c>
+      <c r="U12">
+        <v>327</v>
+      </c>
+      <c r="V12">
+        <v>354</v>
+      </c>
+      <c r="W12">
+        <v>359</v>
+      </c>
+      <c r="AI12">
+        <v>104</v>
+      </c>
+      <c r="AJ12">
+        <v>203.21963659547339</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>13.79</v>
+      </c>
+      <c r="AM12">
+        <v>1.2432260121134839</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13">
+        <v>9485904</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>284</v>
+      </c>
+      <c r="E13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" t="s">
+        <v>285</v>
+      </c>
+      <c r="G13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13">
+        <v>269</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>271</v>
+      </c>
+      <c r="M13">
+        <v>3171</v>
+      </c>
+      <c r="N13">
+        <v>97</v>
+      </c>
+      <c r="O13">
+        <v>48</v>
+      </c>
+      <c r="P13">
+        <v>24</v>
+      </c>
+      <c r="Q13">
+        <v>24</v>
+      </c>
+      <c r="R13">
+        <v>15.8</v>
+      </c>
+      <c r="S13">
+        <v>345</v>
+      </c>
+      <c r="T13">
+        <v>342</v>
+      </c>
+      <c r="U13">
+        <v>319</v>
+      </c>
+      <c r="V13">
+        <v>330</v>
+      </c>
+      <c r="W13">
+        <v>345</v>
+      </c>
+      <c r="AI13">
+        <v>104</v>
+      </c>
+      <c r="AJ13">
+        <v>207.61063807421419</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>11.21</v>
+      </c>
+      <c r="AM13">
+        <v>1.229895931882687</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14">
+        <v>9442392</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>286</v>
+      </c>
+      <c r="E14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" t="s">
+        <v>286</v>
+      </c>
+      <c r="G14" t="s">
+        <v>294</v>
+      </c>
+      <c r="H14" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14">
+        <v>40</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>48</v>
+      </c>
+      <c r="M14">
+        <v>3090</v>
+      </c>
+      <c r="N14">
+        <v>54.24</v>
+      </c>
+      <c r="O14">
+        <v>28.8</v>
+      </c>
+      <c r="P14">
+        <v>2</v>
+      </c>
+      <c r="Q14">
+        <v>10</v>
+      </c>
+      <c r="R14">
+        <v>0.89</v>
+      </c>
+      <c r="AI14">
+        <v>11</v>
+      </c>
+      <c r="AJ14">
+        <v>144.01294498381881</v>
+      </c>
+      <c r="AK14">
+        <v>10</v>
+      </c>
+      <c r="AL14">
+        <v>8</v>
+      </c>
+      <c r="AM14">
+        <v>1.601941747572815</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15">
+        <v>9442392</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>281</v>
+      </c>
+      <c r="E15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" t="s">
+        <v>282</v>
+      </c>
+      <c r="G15" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15">
+        <v>256</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>264</v>
+      </c>
+      <c r="M15">
+        <v>4954</v>
+      </c>
+      <c r="N15">
+        <v>72.69</v>
+      </c>
+      <c r="O15">
+        <v>46.1</v>
+      </c>
+      <c r="P15">
+        <v>24</v>
+      </c>
+      <c r="Q15">
+        <v>24</v>
+      </c>
+      <c r="R15">
+        <v>21.4</v>
+      </c>
+      <c r="S15">
+        <v>365</v>
+      </c>
+      <c r="T15">
+        <v>358</v>
+      </c>
+      <c r="U15">
+        <v>340</v>
+      </c>
+      <c r="V15">
+        <v>332</v>
+      </c>
+      <c r="W15">
+        <v>380</v>
+      </c>
+      <c r="X15">
+        <v>330</v>
+      </c>
+      <c r="AI15">
+        <v>130</v>
+      </c>
+      <c r="AJ15">
+        <v>179.98923428879019</v>
+      </c>
+      <c r="AK15">
+        <v>24</v>
+      </c>
+      <c r="AL15">
+        <v>10.7</v>
+      </c>
+      <c r="AM15">
+        <v>0.98405329027048849</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16">
+        <v>9442392</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" t="s">
+        <v>283</v>
+      </c>
+      <c r="G16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16">
+        <v>260</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>256</v>
+      </c>
+      <c r="M16">
+        <v>4958</v>
+      </c>
+      <c r="N16">
+        <v>71.2</v>
+      </c>
+      <c r="O16">
+        <v>46.2</v>
+      </c>
+      <c r="P16">
+        <v>24</v>
+      </c>
+      <c r="Q16">
+        <v>24</v>
+      </c>
+      <c r="R16">
+        <v>21.42</v>
+      </c>
+      <c r="S16">
+        <v>362</v>
+      </c>
+      <c r="T16">
+        <v>368</v>
+      </c>
+      <c r="U16">
+        <v>338</v>
+      </c>
+      <c r="V16">
+        <v>329</v>
+      </c>
+      <c r="W16">
+        <v>376</v>
+      </c>
+      <c r="X16">
+        <v>333</v>
+      </c>
+      <c r="AI16">
+        <v>130</v>
+      </c>
+      <c r="AJ16">
+        <v>180.0121016538927</v>
+      </c>
+      <c r="AK16">
+        <v>24</v>
+      </c>
+      <c r="AL16">
+        <v>10.75</v>
+      </c>
+      <c r="AM16">
+        <v>0.98325937878176684</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17">
+        <v>9442392</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>283</v>
+      </c>
+      <c r="E17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" t="s">
+        <v>284</v>
+      </c>
+      <c r="G17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" t="s">
+        <v>86</v>
+      </c>
+      <c r="J17">
+        <v>253</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>256</v>
+      </c>
+      <c r="M17">
+        <v>4641</v>
+      </c>
+      <c r="N17">
+        <v>69.94</v>
+      </c>
+      <c r="O17">
+        <v>43.2</v>
+      </c>
+      <c r="P17">
+        <v>24</v>
+      </c>
+      <c r="Q17">
+        <v>24</v>
+      </c>
+      <c r="R17">
+        <v>20.05</v>
+      </c>
+      <c r="S17">
+        <v>342</v>
+      </c>
+      <c r="T17">
+        <v>345</v>
+      </c>
+      <c r="U17">
+        <v>320</v>
+      </c>
+      <c r="V17">
+        <v>315</v>
+      </c>
+      <c r="W17">
+        <v>349</v>
+      </c>
+      <c r="X17">
+        <v>305</v>
+      </c>
+      <c r="AI17">
+        <v>122</v>
+      </c>
+      <c r="AJ17">
+        <v>180.0079005961359</v>
+      </c>
+      <c r="AK17">
+        <v>24</v>
+      </c>
+      <c r="AL17">
+        <v>10.54</v>
+      </c>
+      <c r="AM17">
+        <v>0.98577892695539759</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18">
+        <v>9442392</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>284</v>
+      </c>
+      <c r="E18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" t="s">
+        <v>285</v>
+      </c>
+      <c r="G18" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" t="s">
+        <v>308</v>
+      </c>
+      <c r="I18" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18">
+        <v>250</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>256</v>
+      </c>
+      <c r="M18">
+        <v>4907</v>
+      </c>
+      <c r="N18">
+        <v>71.34</v>
+      </c>
+      <c r="O18">
+        <v>45.7</v>
+      </c>
+      <c r="P18">
+        <v>24</v>
+      </c>
+      <c r="Q18">
+        <v>24</v>
+      </c>
+      <c r="R18">
+        <v>21.2</v>
+      </c>
+      <c r="S18">
+        <v>362</v>
+      </c>
+      <c r="T18">
+        <v>365</v>
+      </c>
+      <c r="U18">
+        <v>332</v>
+      </c>
+      <c r="V18">
+        <v>334</v>
+      </c>
+      <c r="W18">
+        <v>377</v>
+      </c>
+      <c r="X18">
+        <v>327</v>
+      </c>
+      <c r="AI18">
+        <v>128</v>
+      </c>
+      <c r="AJ18">
+        <v>180.01494463691321</v>
+      </c>
+      <c r="AK18">
+        <v>24</v>
+      </c>
+      <c r="AL18">
+        <v>10.41</v>
+      </c>
+      <c r="AM18">
+        <v>0.97819441614020786</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19">
+        <v>9442392</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>285</v>
+      </c>
+      <c r="E19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" t="s">
+        <v>279</v>
+      </c>
+      <c r="G19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19">
+        <v>258</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>252</v>
+      </c>
+      <c r="M19">
+        <v>4907</v>
+      </c>
+      <c r="N19">
+        <v>71.19</v>
+      </c>
+      <c r="O19">
+        <v>45.7</v>
+      </c>
+      <c r="P19">
+        <v>24</v>
+      </c>
+      <c r="Q19">
+        <v>24</v>
+      </c>
+      <c r="R19">
+        <v>21.2</v>
+      </c>
+      <c r="S19">
+        <v>365</v>
+      </c>
+      <c r="T19">
+        <v>360</v>
+      </c>
+      <c r="U19">
+        <v>339</v>
+      </c>
+      <c r="V19">
+        <v>329</v>
+      </c>
+      <c r="W19">
+        <v>379</v>
+      </c>
+      <c r="X19">
+        <v>319</v>
+      </c>
+      <c r="AI19">
+        <v>128</v>
+      </c>
+      <c r="AJ19">
+        <v>180.01494463691321</v>
+      </c>
+      <c r="AK19">
+        <v>24</v>
+      </c>
+      <c r="AL19">
+        <v>10.75</v>
+      </c>
+      <c r="AM19">
+        <v>0.97819441614020786</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20">
+        <v>9442392</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" t="s">
+        <v>279</v>
+      </c>
+      <c r="E20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20">
+        <v>269</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>272</v>
+      </c>
+      <c r="M20">
+        <v>4968</v>
+      </c>
+      <c r="N20">
+        <v>72</v>
+      </c>
+      <c r="O20">
+        <v>46.3</v>
+      </c>
+      <c r="P20">
+        <v>24</v>
+      </c>
+      <c r="Q20">
+        <v>24</v>
+      </c>
+      <c r="R20">
+        <v>21.46</v>
+      </c>
+      <c r="S20">
+        <v>354</v>
+      </c>
+      <c r="T20">
+        <v>351</v>
+      </c>
+      <c r="U20">
+        <v>333</v>
+      </c>
+      <c r="V20">
+        <v>326</v>
+      </c>
+      <c r="W20">
+        <v>369</v>
+      </c>
+      <c r="X20">
+        <v>320</v>
+      </c>
+      <c r="AI20">
+        <v>130</v>
+      </c>
+      <c r="AJ20">
+        <v>179.98523886205049</v>
+      </c>
+      <c r="AK20">
+        <v>24</v>
+      </c>
+      <c r="AL20">
+        <v>11.2</v>
+      </c>
+      <c r="AM20">
+        <v>0.981280193236715</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21">
+        <v>9640994</v>
+      </c>
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" t="s">
+        <v>286</v>
+      </c>
+      <c r="E21" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" t="s">
+        <v>281</v>
+      </c>
+      <c r="G21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H21">
+        <v>99</v>
+      </c>
+      <c r="I21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21">
+        <v>317</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>317</v>
+      </c>
+      <c r="M21">
+        <v>5900</v>
+      </c>
+      <c r="N21">
+        <v>77.239999999999995</v>
+      </c>
+      <c r="O21">
+        <v>45.38</v>
+      </c>
+      <c r="P21">
+        <v>24</v>
+      </c>
+      <c r="Q21">
+        <v>24</v>
+      </c>
+      <c r="R21">
+        <v>24.6</v>
+      </c>
+      <c r="S21">
+        <v>311</v>
+      </c>
+      <c r="T21">
+        <v>307</v>
+      </c>
+      <c r="U21">
+        <v>342</v>
+      </c>
+      <c r="V21">
+        <v>308</v>
+      </c>
+      <c r="W21">
+        <v>318</v>
+      </c>
+      <c r="X21">
+        <v>340</v>
+      </c>
+      <c r="AI21">
+        <v>159</v>
+      </c>
+      <c r="AJ21">
+        <v>173.72881355932199</v>
+      </c>
+      <c r="AK21">
+        <v>24</v>
+      </c>
+      <c r="AL21">
+        <v>13.21</v>
+      </c>
+      <c r="AM21">
+        <v>1.0105932203389829</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22">
+        <v>9640994</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" t="s">
+        <v>281</v>
+      </c>
+      <c r="E22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" t="s">
+        <v>282</v>
+      </c>
+      <c r="G22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H22">
+        <v>99</v>
+      </c>
+      <c r="I22" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22">
+        <v>318</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>318</v>
+      </c>
+      <c r="M22">
+        <v>5900</v>
+      </c>
+      <c r="N22">
+        <v>77.260000000000005</v>
+      </c>
+      <c r="O22">
+        <v>45.38</v>
+      </c>
+      <c r="P22">
+        <v>24</v>
+      </c>
+      <c r="Q22">
+        <v>24</v>
+      </c>
+      <c r="R22">
+        <v>25.1</v>
+      </c>
+      <c r="S22">
+        <v>314</v>
+      </c>
+      <c r="T22">
+        <v>315</v>
+      </c>
+      <c r="U22">
+        <v>350</v>
+      </c>
+      <c r="V22">
+        <v>319</v>
+      </c>
+      <c r="W22">
+        <v>321</v>
+      </c>
+      <c r="X22">
+        <v>342</v>
+      </c>
+      <c r="AI22">
+        <v>177.3</v>
+      </c>
+      <c r="AJ22">
+        <v>177.25988700564969</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>13.25</v>
+      </c>
+      <c r="AM22">
+        <v>1.126906779661017</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23">
+        <v>9640994</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>282</v>
+      </c>
+      <c r="E23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" t="s">
+        <v>283</v>
+      </c>
+      <c r="G23" t="s">
+        <v>102</v>
+      </c>
+      <c r="H23">
+        <v>99</v>
+      </c>
+      <c r="I23" t="s">
+        <v>94</v>
+      </c>
+      <c r="J23">
+        <v>320</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>320</v>
+      </c>
+      <c r="M23">
+        <v>5900</v>
+      </c>
+      <c r="N23">
+        <v>77.38</v>
+      </c>
+      <c r="O23">
+        <v>45.38</v>
+      </c>
+      <c r="P23">
+        <v>24</v>
+      </c>
+      <c r="Q23">
+        <v>24</v>
+      </c>
+      <c r="R23">
+        <v>24.9</v>
+      </c>
+      <c r="S23">
+        <v>317</v>
+      </c>
+      <c r="T23">
+        <v>312</v>
+      </c>
+      <c r="U23">
+        <v>345</v>
+      </c>
+      <c r="V23">
+        <v>315</v>
+      </c>
+      <c r="W23">
+        <v>318</v>
+      </c>
+      <c r="X23">
+        <v>339</v>
+      </c>
+      <c r="AI23">
+        <v>162</v>
+      </c>
+      <c r="AJ23">
+        <v>175.84745762711859</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>13.33</v>
+      </c>
+      <c r="AM23">
+        <v>1.029661016949152</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24">
+        <v>9640994</v>
+      </c>
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" t="s">
+        <v>283</v>
+      </c>
+      <c r="E24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" t="s">
+        <v>284</v>
+      </c>
+      <c r="G24" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24">
+        <v>99</v>
+      </c>
+      <c r="I24" t="s">
+        <v>94</v>
+      </c>
+      <c r="J24">
+        <v>317</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>317</v>
+      </c>
+      <c r="M24">
+        <v>6150</v>
+      </c>
+      <c r="N24">
+        <v>77.66</v>
+      </c>
+      <c r="O24">
+        <v>47.31</v>
+      </c>
+      <c r="P24">
+        <v>24</v>
+      </c>
+      <c r="Q24">
+        <v>24</v>
+      </c>
+      <c r="R24">
+        <v>25.4</v>
+      </c>
+      <c r="S24">
+        <v>310</v>
+      </c>
+      <c r="T24">
+        <v>305</v>
+      </c>
+      <c r="U24">
+        <v>334</v>
+      </c>
+      <c r="V24">
+        <v>311</v>
+      </c>
+      <c r="W24">
+        <v>313</v>
+      </c>
+      <c r="X24">
+        <v>335</v>
+      </c>
+      <c r="AI24">
+        <v>164</v>
+      </c>
+      <c r="AJ24">
+        <v>172.0867208672087</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>13.21</v>
+      </c>
+      <c r="AM24">
+        <v>1</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="25" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25">
+        <v>9640994</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>284</v>
+      </c>
+      <c r="E25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" t="s">
+        <v>285</v>
+      </c>
+      <c r="G25" t="s">
+        <v>102</v>
+      </c>
+      <c r="H25">
+        <v>99</v>
+      </c>
+      <c r="I25" t="s">
+        <v>143</v>
+      </c>
+      <c r="J25">
+        <v>310</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>310</v>
+      </c>
+      <c r="M25">
+        <v>5900</v>
+      </c>
+      <c r="N25">
+        <v>75.5</v>
+      </c>
+      <c r="O25">
+        <v>45.38</v>
+      </c>
+      <c r="P25">
+        <v>23</v>
+      </c>
+      <c r="Q25">
+        <v>23</v>
+      </c>
+      <c r="R25">
+        <v>23.65</v>
+      </c>
+      <c r="S25">
+        <v>310</v>
+      </c>
+      <c r="T25">
+        <v>305</v>
+      </c>
+      <c r="U25">
+        <v>334</v>
+      </c>
+      <c r="V25">
+        <v>311</v>
+      </c>
+      <c r="W25">
+        <v>313</v>
+      </c>
+      <c r="X25">
+        <v>335</v>
+      </c>
+      <c r="AI25">
+        <v>151</v>
+      </c>
+      <c r="AJ25">
+        <v>174.28150331613861</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>13.48</v>
+      </c>
+      <c r="AM25">
+        <v>1.001473839351511</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="26" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26">
+        <v>9640994</v>
+      </c>
+      <c r="C26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" t="s">
+        <v>285</v>
+      </c>
+      <c r="E26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" t="s">
+        <v>279</v>
+      </c>
+      <c r="G26" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26">
+        <v>99</v>
+      </c>
+      <c r="I26" t="s">
+        <v>94</v>
+      </c>
+      <c r="J26">
+        <v>320</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>320</v>
+      </c>
+      <c r="M26">
+        <v>6000</v>
+      </c>
+      <c r="N26">
+        <v>76.81</v>
+      </c>
+      <c r="O26">
+        <v>46.15</v>
+      </c>
+      <c r="P26">
+        <v>24</v>
+      </c>
+      <c r="Q26">
+        <v>24</v>
+      </c>
+      <c r="R26">
+        <v>24.85</v>
+      </c>
+      <c r="S26">
+        <v>313</v>
+      </c>
+      <c r="T26">
+        <v>310</v>
+      </c>
+      <c r="U26">
+        <v>338</v>
+      </c>
+      <c r="V26">
+        <v>311</v>
+      </c>
+      <c r="W26">
+        <v>314</v>
+      </c>
+      <c r="X26">
+        <v>332</v>
+      </c>
+      <c r="AI26">
+        <v>164</v>
+      </c>
+      <c r="AJ26">
+        <v>172.56944444444451</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>13.33</v>
+      </c>
+      <c r="AM26">
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27">
+        <v>9640994</v>
+      </c>
+      <c r="C27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>279</v>
+      </c>
+      <c r="E27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27" t="s">
+        <v>280</v>
+      </c>
+      <c r="G27" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27">
+        <v>99</v>
+      </c>
+      <c r="I27" t="s">
+        <v>129</v>
+      </c>
+      <c r="J27">
+        <v>305</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>305</v>
+      </c>
+      <c r="M27">
+        <v>6000</v>
+      </c>
+      <c r="N27">
+        <v>76.17</v>
+      </c>
+      <c r="O27">
+        <v>46.15</v>
+      </c>
+      <c r="P27">
+        <v>23</v>
+      </c>
+      <c r="Q27">
+        <v>23</v>
+      </c>
+      <c r="R27">
+        <v>23.3</v>
+      </c>
+      <c r="S27">
+        <v>308</v>
+      </c>
+      <c r="T27">
+        <v>310</v>
+      </c>
+      <c r="U27">
+        <v>343</v>
+      </c>
+      <c r="V27">
+        <v>308</v>
+      </c>
+      <c r="W27">
+        <v>313</v>
+      </c>
+      <c r="X27">
+        <v>333</v>
+      </c>
+      <c r="AI27">
+        <v>150</v>
+      </c>
+      <c r="AJ27">
+        <v>168.84057971014491</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>13.26</v>
+      </c>
+      <c r="AM27">
+        <v>0.97826086956521741</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="28" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28">
+        <v>9506540</v>
+      </c>
+      <c r="C28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" t="s">
+        <v>285</v>
+      </c>
+      <c r="E28" t="s">
+        <v>309</v>
+      </c>
+      <c r="F28" t="s">
+        <v>279</v>
+      </c>
+      <c r="G28" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28">
+        <v>151</v>
+      </c>
+      <c r="I28" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>25</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>17.2</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>16.2</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="29" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29">
+        <v>9506540</v>
+      </c>
+      <c r="C29" t="s">
+        <v>145</v>
+      </c>
+      <c r="D29" t="s">
+        <v>279</v>
+      </c>
+      <c r="E29" t="s">
+        <v>311</v>
+      </c>
+      <c r="F29" t="s">
+        <v>280</v>
+      </c>
+      <c r="G29" t="s">
+        <v>312</v>
+      </c>
+      <c r="H29">
+        <v>151</v>
+      </c>
+      <c r="I29" t="s">
+        <v>42</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>9</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>16.2</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="30" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>200</v>
+      </c>
+      <c r="B30">
+        <v>9603609</v>
+      </c>
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" t="s">
+        <v>282</v>
+      </c>
+      <c r="E30" t="s">
+        <v>314</v>
+      </c>
+      <c r="F30" t="s">
+        <v>283</v>
+      </c>
+      <c r="G30" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30">
+        <v>22</v>
+      </c>
+      <c r="I30" t="s">
+        <v>45</v>
+      </c>
+      <c r="J30">
+        <v>291</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>329</v>
+      </c>
+      <c r="M30">
+        <v>6201</v>
+      </c>
+      <c r="N30">
+        <v>61.4</v>
+      </c>
+      <c r="O30">
+        <v>28.9</v>
+      </c>
+      <c r="P30">
+        <v>21</v>
+      </c>
+      <c r="Q30">
+        <v>21.5</v>
+      </c>
+      <c r="R30">
+        <v>25.8</v>
+      </c>
+      <c r="S30">
+        <v>310</v>
+      </c>
+      <c r="T30">
+        <v>37</v>
+      </c>
+      <c r="U30">
+        <v>328</v>
+      </c>
+      <c r="V30">
+        <v>333</v>
+      </c>
+      <c r="W30">
+        <v>317</v>
+      </c>
+      <c r="X30">
+        <v>307</v>
+      </c>
+      <c r="Y30">
+        <v>315</v>
+      </c>
+      <c r="AI30">
+        <v>210</v>
+      </c>
+      <c r="AJ30">
+        <v>198.12472642661319</v>
+      </c>
+      <c r="AK30">
+        <v>21.5</v>
+      </c>
+      <c r="AL30">
+        <v>13.88</v>
+      </c>
+      <c r="AM30">
+        <v>1.4513788098693761</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31">
+        <v>9204726</v>
+      </c>
+      <c r="C31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" t="s">
+        <v>282</v>
+      </c>
+      <c r="E31" t="s">
+        <v>102</v>
+      </c>
+      <c r="F31" t="s">
+        <v>283</v>
+      </c>
+      <c r="G31" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" t="s">
+        <v>316</v>
+      </c>
+      <c r="I31" t="s">
+        <v>42</v>
+      </c>
+      <c r="J31">
+        <v>236.2</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>225.8</v>
+      </c>
+      <c r="M31">
+        <v>4680</v>
+      </c>
+      <c r="N31">
+        <v>457</v>
+      </c>
+      <c r="O31">
+        <v>60</v>
+      </c>
+      <c r="P31">
+        <v>24</v>
+      </c>
+      <c r="Q31">
+        <v>24</v>
+      </c>
+      <c r="R31">
+        <v>12.1</v>
+      </c>
+      <c r="S31">
+        <v>431</v>
+      </c>
+      <c r="T31">
+        <v>489</v>
+      </c>
+      <c r="U31">
+        <v>494</v>
+      </c>
+      <c r="V31">
+        <v>401</v>
+      </c>
+      <c r="W31">
+        <v>383</v>
+      </c>
+      <c r="X31">
+        <v>452</v>
+      </c>
+      <c r="Y31">
+        <v>396</v>
+      </c>
+      <c r="Z31">
+        <v>338</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>107.72792022792019</v>
+      </c>
+      <c r="AK31">
+        <v>24</v>
+      </c>
+      <c r="AL31">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="32" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32">
+        <v>9204726</v>
+      </c>
+      <c r="C32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" t="s">
+        <v>283</v>
+      </c>
+      <c r="E32" t="s">
+        <v>102</v>
+      </c>
+      <c r="F32" t="s">
+        <v>284</v>
+      </c>
+      <c r="G32" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" t="s">
+        <v>318</v>
+      </c>
+      <c r="I32" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32">
+        <v>236</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>264</v>
+      </c>
+      <c r="M32">
+        <v>4680</v>
+      </c>
+      <c r="N32">
+        <v>457</v>
+      </c>
+      <c r="O32">
+        <v>60</v>
+      </c>
+      <c r="P32">
+        <v>24</v>
+      </c>
+      <c r="Q32">
+        <v>24</v>
+      </c>
+      <c r="R32">
+        <v>12.1</v>
+      </c>
+      <c r="S32">
+        <v>424</v>
+      </c>
+      <c r="T32">
+        <v>454</v>
+      </c>
+      <c r="U32">
+        <v>509</v>
+      </c>
+      <c r="V32">
+        <v>401</v>
+      </c>
+      <c r="W32">
+        <v>407</v>
+      </c>
+      <c r="X32">
+        <v>467</v>
+      </c>
+      <c r="Y32">
+        <v>399</v>
+      </c>
+      <c r="Z32">
+        <v>365</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>107.72792022792019</v>
+      </c>
+      <c r="AK32">
+        <v>24</v>
+      </c>
+      <c r="AL32">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="33" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33">
+        <v>9204726</v>
+      </c>
+      <c r="C33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" t="s">
+        <v>284</v>
+      </c>
+      <c r="E33" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" t="s">
+        <v>285</v>
+      </c>
+      <c r="G33" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" t="s">
+        <v>318</v>
+      </c>
+      <c r="I33" t="s">
+        <v>42</v>
+      </c>
+      <c r="J33">
+        <v>260.60000000000002</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>260.14999999999998</v>
+      </c>
+      <c r="M33">
+        <v>4680</v>
+      </c>
+      <c r="N33">
+        <v>460</v>
+      </c>
+      <c r="O33">
+        <v>60</v>
+      </c>
+      <c r="P33">
+        <v>24</v>
+      </c>
+      <c r="Q33">
+        <v>24</v>
+      </c>
+      <c r="R33">
+        <v>12.5</v>
+      </c>
+      <c r="S33">
+        <v>431</v>
+      </c>
+      <c r="T33">
+        <v>489</v>
+      </c>
+      <c r="U33">
+        <v>494</v>
+      </c>
+      <c r="V33">
+        <v>401</v>
+      </c>
+      <c r="W33">
+        <v>383</v>
+      </c>
+      <c r="X33">
+        <v>452</v>
+      </c>
+      <c r="Y33">
+        <v>396</v>
+      </c>
+      <c r="Z33">
+        <v>338</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>111.2891737891738</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>11.3</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="34" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>161</v>
+      </c>
+      <c r="B34">
+        <v>9204726</v>
+      </c>
+      <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" t="s">
+        <v>285</v>
+      </c>
+      <c r="E34" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" t="s">
+        <v>279</v>
+      </c>
+      <c r="G34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" t="s">
+        <v>316</v>
+      </c>
+      <c r="I34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34">
+        <v>243.8</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>259.10000000000002</v>
+      </c>
+      <c r="M34">
+        <v>5070</v>
+      </c>
+      <c r="N34">
+        <v>459</v>
+      </c>
+      <c r="O34">
+        <v>65</v>
+      </c>
+      <c r="P34">
+        <v>24</v>
+      </c>
+      <c r="Q34">
+        <v>23</v>
+      </c>
+      <c r="R34">
+        <v>11.9</v>
+      </c>
+      <c r="S34">
+        <v>431</v>
+      </c>
+      <c r="T34">
+        <v>489</v>
+      </c>
+      <c r="U34">
+        <v>494</v>
+      </c>
+      <c r="V34">
+        <v>401</v>
+      </c>
+      <c r="W34">
+        <v>383</v>
+      </c>
+      <c r="X34">
+        <v>452</v>
+      </c>
+      <c r="Y34">
+        <v>396</v>
+      </c>
+      <c r="Z34">
+        <v>338</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>97.797501643655494</v>
+      </c>
+      <c r="AK34">
+        <v>24</v>
+      </c>
+      <c r="AL34">
+        <v>10.6</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="35" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35">
+        <v>9204726</v>
+      </c>
+      <c r="C35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" t="s">
+        <v>279</v>
+      </c>
+      <c r="E35" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35" t="s">
+        <v>280</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" t="s">
+        <v>318</v>
+      </c>
+      <c r="I35" t="s">
+        <v>42</v>
+      </c>
+      <c r="J35">
+        <v>267.8</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>269.39999999999998</v>
+      </c>
+      <c r="M35">
+        <v>5070</v>
+      </c>
+      <c r="N35">
+        <v>459</v>
+      </c>
+      <c r="O35">
+        <v>65</v>
+      </c>
+      <c r="P35">
+        <v>24</v>
+      </c>
+      <c r="Q35">
+        <v>24</v>
+      </c>
+      <c r="R35">
+        <v>11.5</v>
+      </c>
+      <c r="S35">
+        <v>431</v>
+      </c>
+      <c r="T35">
+        <v>489</v>
+      </c>
+      <c r="U35">
+        <v>494</v>
+      </c>
+      <c r="V35">
+        <v>401</v>
+      </c>
+      <c r="W35">
+        <v>383</v>
+      </c>
+      <c r="X35">
+        <v>452</v>
+      </c>
+      <c r="Y35">
+        <v>396</v>
+      </c>
+      <c r="Z35">
+        <v>338</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>94.510190664036813</v>
+      </c>
+      <c r="AK35">
+        <v>24</v>
+      </c>
+      <c r="AL35">
+        <v>11.1</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36">
+        <v>9448138</v>
+      </c>
+      <c r="C36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" t="s">
+        <v>286</v>
+      </c>
+      <c r="E36" t="s">
+        <v>208</v>
+      </c>
+      <c r="F36" t="s">
+        <v>281</v>
+      </c>
+      <c r="G36" t="s">
+        <v>208</v>
+      </c>
+      <c r="H36" t="s">
+        <v>323</v>
+      </c>
+      <c r="I36" t="s">
+        <v>45</v>
+      </c>
+      <c r="J36">
+        <v>316</v>
+      </c>
+      <c r="K36">
+        <v>-1</v>
+      </c>
+      <c r="L36">
+        <v>468.7</v>
+      </c>
+      <c r="M36">
+        <v>6771</v>
+      </c>
+      <c r="N36">
+        <v>99.5</v>
+      </c>
+      <c r="O36">
+        <v>47.61</v>
+      </c>
+      <c r="P36">
+        <v>25</v>
+      </c>
+      <c r="Q36">
+        <v>25</v>
+      </c>
+      <c r="R36">
+        <v>35.32</v>
+      </c>
+      <c r="S36">
+        <v>350</v>
+      </c>
+      <c r="T36">
+        <v>340</v>
+      </c>
+      <c r="U36">
+        <v>330</v>
+      </c>
+      <c r="V36">
+        <v>320</v>
+      </c>
+      <c r="W36">
+        <v>325</v>
+      </c>
+      <c r="X36">
+        <v>340</v>
+      </c>
+      <c r="Y36">
+        <v>320</v>
+      </c>
+      <c r="Z36">
+        <v>325</v>
+      </c>
+      <c r="AA36">
+        <v>340</v>
+      </c>
+      <c r="AI36">
+        <v>193</v>
+      </c>
+      <c r="AJ36">
+        <v>208.65455619553981</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>12.64</v>
+      </c>
+      <c r="AM36">
+        <v>1.0261408949933539</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="37" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>207</v>
+      </c>
+      <c r="B37">
+        <v>9448138</v>
+      </c>
+      <c r="C37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" t="s">
+        <v>281</v>
+      </c>
+      <c r="E37" t="s">
+        <v>208</v>
+      </c>
+      <c r="F37" t="s">
+        <v>282</v>
+      </c>
+      <c r="G37" t="s">
+        <v>208</v>
+      </c>
+      <c r="H37" t="s">
+        <v>323</v>
+      </c>
+      <c r="I37" t="s">
+        <v>45</v>
+      </c>
+      <c r="J37">
+        <v>307</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>447</v>
+      </c>
+      <c r="M37">
+        <v>6046</v>
+      </c>
+      <c r="N37">
+        <v>98.85</v>
+      </c>
+      <c r="O37">
+        <v>42.52</v>
+      </c>
+      <c r="P37">
+        <v>24</v>
+      </c>
+      <c r="Q37">
+        <v>24</v>
+      </c>
+      <c r="R37">
+        <v>32.14</v>
+      </c>
+      <c r="S37">
+        <v>345</v>
+      </c>
+      <c r="T37">
+        <v>340</v>
+      </c>
+      <c r="U37">
+        <v>320</v>
+      </c>
+      <c r="V37">
+        <v>320</v>
+      </c>
+      <c r="W37">
+        <v>320</v>
+      </c>
+      <c r="X37">
+        <v>340</v>
+      </c>
+      <c r="Y37">
+        <v>330</v>
+      </c>
+      <c r="Z37">
+        <v>325</v>
+      </c>
+      <c r="AA37">
+        <v>340</v>
+      </c>
+      <c r="AI37">
+        <v>173</v>
+      </c>
+      <c r="AJ37">
+        <v>221.49630609769551</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>12.79</v>
+      </c>
+      <c r="AM37">
+        <v>1.0730234866027131</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="38" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38">
+        <v>9448138</v>
+      </c>
+      <c r="C38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" t="s">
+        <v>282</v>
+      </c>
+      <c r="E38" t="s">
+        <v>208</v>
+      </c>
+      <c r="F38" t="s">
+        <v>283</v>
+      </c>
+      <c r="G38" t="s">
+        <v>208</v>
+      </c>
+      <c r="H38" t="s">
+        <v>326</v>
+      </c>
+      <c r="I38" t="s">
+        <v>45</v>
+      </c>
+      <c r="J38">
+        <v>372</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>465.3</v>
+      </c>
+      <c r="M38">
+        <v>6478</v>
+      </c>
+      <c r="N38">
+        <v>102.9</v>
+      </c>
+      <c r="O38">
+        <v>45.55</v>
+      </c>
+      <c r="P38">
+        <v>24</v>
+      </c>
+      <c r="Q38">
+        <v>24</v>
+      </c>
+      <c r="R38">
+        <v>33.18</v>
+      </c>
+      <c r="S38">
+        <v>355</v>
+      </c>
+      <c r="T38">
+        <v>350</v>
+      </c>
+      <c r="U38">
+        <v>330</v>
+      </c>
+      <c r="V38">
+        <v>330</v>
+      </c>
+      <c r="W38">
+        <v>330</v>
+      </c>
+      <c r="X38">
+        <v>350</v>
+      </c>
+      <c r="Y38">
+        <v>330</v>
+      </c>
+      <c r="Z38">
+        <v>330</v>
+      </c>
+      <c r="AA38">
+        <v>345</v>
+      </c>
+      <c r="AI38">
+        <v>180</v>
+      </c>
+      <c r="AJ38">
+        <v>213.41463414634151</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>15.5</v>
+      </c>
+      <c r="AM38">
+        <v>1.0419882679839461</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39">
+        <v>9448138</v>
+      </c>
+      <c r="C39" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" t="s">
+        <v>283</v>
+      </c>
+      <c r="E39" t="s">
+        <v>208</v>
+      </c>
+      <c r="F39" t="s">
+        <v>284</v>
+      </c>
+      <c r="G39" t="s">
+        <v>208</v>
+      </c>
+      <c r="H39" t="s">
+        <v>323</v>
+      </c>
+      <c r="I39" t="s">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>404</v>
+      </c>
+      <c r="K39">
+        <v>-1</v>
+      </c>
+      <c r="L39">
+        <v>490</v>
+      </c>
+      <c r="M39">
+        <v>6954</v>
+      </c>
+      <c r="N39">
+        <v>104</v>
+      </c>
+      <c r="O39">
+        <v>46</v>
+      </c>
+      <c r="P39">
+        <v>25</v>
+      </c>
+      <c r="Q39">
+        <v>25</v>
+      </c>
+      <c r="R39">
+        <v>34.6</v>
+      </c>
+      <c r="S39">
+        <v>360</v>
+      </c>
+      <c r="T39">
+        <v>350</v>
+      </c>
+      <c r="U39">
+        <v>340</v>
+      </c>
+      <c r="V39">
+        <v>330</v>
+      </c>
+      <c r="W39">
+        <v>325</v>
+      </c>
+      <c r="X39">
+        <v>360</v>
+      </c>
+      <c r="Y39">
+        <v>335</v>
+      </c>
+      <c r="Z39">
+        <v>330</v>
+      </c>
+      <c r="AA39">
+        <v>345</v>
+      </c>
+      <c r="AI39">
+        <v>190</v>
+      </c>
+      <c r="AJ39">
+        <v>199.02214552775379</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>16.16</v>
+      </c>
+      <c r="AM39">
+        <v>0.98360655737704916</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="40" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40">
+        <v>9448138</v>
+      </c>
+      <c r="C40" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" t="s">
+        <v>285</v>
+      </c>
+      <c r="E40" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" t="s">
+        <v>279</v>
+      </c>
+      <c r="G40" t="s">
+        <v>208</v>
+      </c>
+      <c r="H40" t="s">
+        <v>323</v>
+      </c>
+      <c r="I40" t="s">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>5.9</v>
+      </c>
+      <c r="Q40">
+        <v>24</v>
+      </c>
+      <c r="R40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AI40">
+        <v>33</v>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>1.65</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="41" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41">
+        <v>9431836</v>
+      </c>
+      <c r="C41" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" t="s">
+        <v>284</v>
+      </c>
+      <c r="E41" t="s">
+        <v>330</v>
+      </c>
+      <c r="F41" t="s">
+        <v>284</v>
+      </c>
+      <c r="G41" t="s">
+        <v>331</v>
+      </c>
+      <c r="H41" t="s">
+        <v>332</v>
+      </c>
+      <c r="I41" t="s">
+        <v>139</v>
+      </c>
+      <c r="J41">
+        <v>13</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>13</v>
+      </c>
+      <c r="M41">
+        <v>2582.9</v>
+      </c>
+      <c r="N41">
+        <v>66.3</v>
+      </c>
+      <c r="O41">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="P41">
+        <v>1.4</v>
+      </c>
+      <c r="Q41">
+        <v>1.6</v>
+      </c>
+      <c r="R41">
+        <v>0.6</v>
+      </c>
+      <c r="AI41">
+        <v>8</v>
+      </c>
+      <c r="AJ41">
+        <v>165.92645033544801</v>
+      </c>
+      <c r="AK41">
+        <v>1.6</v>
+      </c>
+      <c r="AL41">
+        <v>8.5</v>
+      </c>
+      <c r="AM41">
+        <v>1.9911174040253761</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="42" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42">
+        <v>9431836</v>
+      </c>
+      <c r="C42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" t="s">
+        <v>284</v>
+      </c>
+      <c r="E42" t="s">
+        <v>102</v>
+      </c>
+      <c r="F42" t="s">
+        <v>285</v>
+      </c>
+      <c r="G42" t="s">
+        <v>334</v>
+      </c>
+      <c r="H42" t="s">
+        <v>332</v>
+      </c>
+      <c r="I42" t="s">
+        <v>139</v>
+      </c>
+      <c r="J42">
+        <v>345</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>339</v>
+      </c>
+      <c r="M42">
+        <v>6109.3</v>
+      </c>
+      <c r="N42">
+        <v>102.8</v>
+      </c>
+      <c r="O42">
+        <v>42.9</v>
+      </c>
+      <c r="P42">
+        <v>21.6</v>
+      </c>
+      <c r="Q42">
+        <v>21.6</v>
+      </c>
+      <c r="R42">
+        <v>25.2</v>
+      </c>
+      <c r="S42">
+        <v>352</v>
+      </c>
+      <c r="T42">
+        <v>360</v>
+      </c>
+      <c r="U42">
+        <v>361</v>
+      </c>
+      <c r="V42">
+        <v>363</v>
+      </c>
+      <c r="W42">
+        <v>354</v>
+      </c>
+      <c r="X42">
+        <v>368</v>
+      </c>
+      <c r="Y42">
+        <v>353</v>
+      </c>
+      <c r="Z42">
+        <v>364</v>
+      </c>
+      <c r="AA42">
+        <v>368</v>
+      </c>
+      <c r="AI42">
+        <v>143</v>
+      </c>
+      <c r="AJ42">
+        <v>190.96568619427211</v>
+      </c>
+      <c r="AK42">
+        <v>6</v>
+      </c>
+      <c r="AL42">
+        <v>15.97</v>
+      </c>
+      <c r="AM42">
+        <v>0.97528904020646112</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC02271-412F-4019-8A2C-3CDDF933B004}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="12" max="12" width="30.453125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>269</v>
       </c>
@@ -15183,10 +19191,13 @@
         <v>273</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>100</v>
       </c>
@@ -15202,11 +19213,15 @@
       <c r="E2" s="7">
         <v>2</v>
       </c>
-      <c r="F2" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5">
+        <f>SUM(B2:F2)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>39</v>
       </c>
@@ -15222,11 +19237,15 @@
       <c r="E3" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="7">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G24" si="0">SUM(B3:F3)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>110</v>
       </c>
@@ -15242,11 +19261,15 @@
       <c r="E4" s="7">
         <v>0</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>44</v>
       </c>
@@ -15262,11 +19285,15 @@
       <c r="E5" s="7">
         <v>0</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>57</v>
       </c>
@@ -15282,11 +19309,15 @@
       <c r="E6" s="7">
         <v>1</v>
       </c>
-      <c r="F6" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F6" s="7">
+        <v>5</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>65</v>
       </c>
@@ -15302,11 +19333,15 @@
       <c r="E7" s="7">
         <v>3</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>275</v>
       </c>
@@ -15322,11 +19357,15 @@
       <c r="E8" s="7">
         <v>0</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>74</v>
       </c>
@@ -15342,11 +19381,15 @@
       <c r="E9" s="7">
         <v>2</v>
       </c>
-      <c r="F9" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>276</v>
       </c>
@@ -15362,11 +19405,15 @@
       <c r="E10" s="7">
         <v>4</v>
       </c>
-      <c r="F10" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F10" s="7">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>150</v>
       </c>
@@ -15382,11 +19429,15 @@
       <c r="E11" s="7">
         <v>0</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>84</v>
       </c>
@@ -15402,11 +19453,15 @@
       <c r="E12" s="7">
         <v>1</v>
       </c>
-      <c r="F12" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F12" s="7">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>89</v>
       </c>
@@ -15422,11 +19477,15 @@
       <c r="E13" s="7">
         <v>7</v>
       </c>
-      <c r="F13" s="5">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F13" s="7">
+        <v>7</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>248</v>
       </c>
@@ -15442,11 +19501,15 @@
       <c r="E14" s="7">
         <v>3</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>193</v>
       </c>
@@ -15462,11 +19525,15 @@
       <c r="E15" s="7">
         <v>1</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="7">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>93</v>
       </c>
@@ -15482,11 +19549,15 @@
       <c r="E16" s="7">
         <v>0</v>
       </c>
-      <c r="F16" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F16" s="7">
+        <v>7</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>97</v>
       </c>
@@ -15502,11 +19573,15 @@
       <c r="E17" s="7">
         <v>0</v>
       </c>
-      <c r="F17" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F17" s="7">
+        <v>2</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>199</v>
       </c>
@@ -15522,11 +19597,15 @@
       <c r="E18" s="7">
         <v>0</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="7">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>200</v>
       </c>
@@ -15542,11 +19621,15 @@
       <c r="E19" s="7">
         <v>3</v>
       </c>
-      <c r="F19" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="F19" s="7">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>260</v>
       </c>
@@ -15562,11 +19645,15 @@
       <c r="E20" s="7">
         <v>5</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="7">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>161</v>
       </c>
@@ -15582,11 +19669,15 @@
       <c r="E21" s="7">
         <v>0</v>
       </c>
-      <c r="F21" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F21" s="7">
+        <v>5</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>207</v>
       </c>
@@ -15602,11 +19693,15 @@
       <c r="E22" s="7">
         <v>3</v>
       </c>
-      <c r="F22" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F22" s="7">
+        <v>5</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>167</v>
       </c>
@@ -15622,11 +19717,15 @@
       <c r="E23" s="7">
         <v>0</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G23" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>277</v>
       </c>
@@ -15643,7 +19742,12 @@
         <v>40</v>
       </c>
       <c r="F24" s="5">
-        <v>151</v>
+        <f>SUM(F2:F23)</f>
+        <v>41</v>
+      </c>
+      <c r="G24" s="5">
+        <f t="shared" si="0"/>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
